--- a/results/tables/03_env_driven_taxa_clusters/table7_mccv_confusion_matrix.xlsx
+++ b/results/tables/03_env_driven_taxa_clusters/table7_mccv_confusion_matrix.xlsx
@@ -425,64 +425,124 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Pred. Cluster 0</t>
+          <t>% Correct</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Pred. Cluster 1</t>
+          <t>Cluster C1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster C2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster C3</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>True Cluster 0</t>
+          <t>Cluster C1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4245</v>
+        <v>85</v>
       </c>
       <c r="C2" t="n">
-        <v>1755</v>
+        <v>6835</v>
+      </c>
+      <c r="D2" t="n">
+        <v>465</v>
+      </c>
+      <c r="E2" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>True Cluster 1</t>
+          <t>Cluster C2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2257</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>2743</v>
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Cluster C3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>846</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Test Size: 20.0% per iteration</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Note: Combined results from 1,000 cross-validation iterations</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7681</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1465</v>
+      </c>
+      <c r="E5" t="n">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Note: Combined results from 1,000 CV iterations (test size: 20%)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
